--- a/results/Int Task Remove ACC 0.4/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_1_permute.xlsx
@@ -440,217 +440,217 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5247232900745633</v>
+        <v>0.5269550297995305</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5359722903067674</v>
+        <v>0.521562733816662</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5418999458190356</v>
+        <v>0.5212466781908718</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5401519647049717</v>
+        <v>0.5203501122319978</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.539739157357001</v>
+        <v>0.525258649603963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5736538610387265</v>
+        <v>0.525258649603963</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5640754405428416</v>
+        <v>0.5109006940323537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.559534559715163</v>
+        <v>0.5118746613689724</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5567094094274878</v>
+        <v>0.5147191620010836</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5256392063778735</v>
+        <v>0.5147191620010836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5263680693516345</v>
+        <v>0.5144031063752935</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5266841249774246</v>
+        <v>0.5119004618282206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.522169044608994</v>
+        <v>0.5079142908743776</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.520685518202224</v>
+        <v>0.5012964730772207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5121520163058902</v>
+        <v>0.4999870997703759</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5130292319203282</v>
+        <v>0.4973103021233778</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.531618462808638</v>
+        <v>0.4907763358187776</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5266131737144921</v>
+        <v>0.4932725302510385</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5328181841636781</v>
+        <v>0.4925436672772775</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5424675559224954</v>
+        <v>0.4768376377099512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5424675559224954</v>
+        <v>0.4781728114760443</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.541519389045125</v>
+        <v>0.4902925772078743</v>
       </c>
     </row>
     <row r="24">
@@ -660,667 +660,667 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.543293170618437</v>
+        <v>0.491434247529606</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5421515002967053</v>
+        <v>0.4911181919038159</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5438543306070849</v>
+        <v>0.5028316004024871</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5441703862328749</v>
+        <v>0.5031476560282773</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5386297376093294</v>
+        <v>0.4977489099305968</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5385071854279007</v>
+        <v>0.500006450114812</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5392360484016616</v>
+        <v>0.4978263113083413</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5161059366856731</v>
+        <v>0.487738331742305</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5205887664800434</v>
+        <v>0.4907763358187776</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5192729430583864</v>
+        <v>0.4944206506875822</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5298898320390103</v>
+        <v>0.4991614850744343</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5250135452411053</v>
+        <v>0.4998193967852628</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5083657989112206</v>
+        <v>0.4996000928816533</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5388877422018112</v>
+        <v>0.4963427849015712</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5388877422018112</v>
+        <v>0.491576150055471</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4740705384555846</v>
+        <v>0.4990453830078175</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4657563404628602</v>
+        <v>0.4984390722154854</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4537010758791507</v>
+        <v>0.4932338295621662</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4684524884542945</v>
+        <v>0.4770182409246885</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4528690110683971</v>
+        <v>0.4773342965504786</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4549588482674992</v>
+        <v>0.4738576846667871</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4296034469413555</v>
+        <v>0.4811011636007121</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4220632627260765</v>
+        <v>0.4851260352434273</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4271201527387187</v>
+        <v>0.4920728088959984</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4271201527387187</v>
+        <v>0.4872868237054619</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4124590417709435</v>
+        <v>0.4788565236461209</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4124590417709435</v>
+        <v>0.4805077530380041</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3454874996774943</v>
+        <v>0.4776374519466446</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3503444361309631</v>
+        <v>0.4683686369617379</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3404499600092882</v>
+        <v>0.4707680796718182</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3605872184524884</v>
+        <v>0.4543847880492273</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3456681028922315</v>
+        <v>0.4543847880492273</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.350473438427204</v>
+        <v>0.4360535617533992</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3658053613354318</v>
+        <v>0.4655499367888749</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3828981655873475</v>
+        <v>0.4854614412136536</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3643927861915942</v>
+        <v>0.4833458035553033</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.367456590727315</v>
+        <v>0.4833458035553033</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3694948270079207</v>
+        <v>0.4968394437420986</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.379144198766738</v>
+        <v>0.4968394437420986</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3794602543925282</v>
+        <v>0.4987099770375913</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3953146366005315</v>
+        <v>0.5009223664181223</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.3784217859077892</v>
+        <v>0.4969361954642793</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3727585851028148</v>
+        <v>0.49851647359323</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4404138393663407</v>
+        <v>0.4965233881163085</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4404138393663407</v>
+        <v>0.4981036662452591</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4317706855182022</v>
+        <v>0.49851647359323</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4413168554400268</v>
+        <v>0.4974199540751825</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4350473438427204</v>
+        <v>0.4964717871978121</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.449024742640419</v>
+        <v>0.4993678887484197</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.449024742640419</v>
+        <v>0.4993678887484197</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4635762016563895</v>
+        <v>0.4990518331226296</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4635762016563895</v>
+        <v>0.4990518331226296</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4635762016563895</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4649629763409789</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4795982868495059</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4820815810521427</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4708841817384349</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5086302536185144</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5080497432854305</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5073208803116696</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5003225057406022</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5180667715885343</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5223302974792952</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5191697412213938</v>
+        <v>0.4994646404706004</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5240460280192987</v>
+        <v>0.4990518331226296</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4843649216956062</v>
+        <v>0.4990518331226296</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5008320648107536</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
   </sheetData>
